--- a/results/Supplementary_Table_4_BUSTED_PH.xlsx
+++ b/results/Supplementary_Table_4_BUSTED_PH.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,45 +549,125 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>ω0_test_null</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ω0_test_null_P</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ω1_test_null</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ω1_test_null_P</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>ω2_test_null</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ω2_test_null_P</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ω3_test_null</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>ω3_test_null_P</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>ω0_ref_null</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>ω0_ref_null_P</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>ω1_ref_null</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>ω1_ref_null_P</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>ω2_ref_null</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>ω2_ref_null_P</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>ω3_ref_null</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>ω3_ref_null_P</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
           <t>ω_mean_test</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>ω_mean_ref</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>U. diversus gene ID</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>U. diversus GO terms</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>U. diversus gene description</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>P. tepidariorum best BLAST hit LOC</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>P. tepidariorum best BLAST hit description</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>U. diversus best BLAST hit LOC</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>U. diversus best BLAST hit description</t>
         </is>
@@ -677,42 +757,90 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
+        <v>104.5682038267025</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.06201136653871771</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6778578667503111</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.07461500638103125</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.2925386812940222</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.02960345195566666</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>105.9282275983445</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.001687249358133555</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.05098022869338903</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.6973116540983204</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.04972312200142739</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.301001096543546</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2.530139010798623</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>0.1257232976936182</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AR2" t="n">
         <v>0.05090571953790804</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>129221501</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>GO:0004362 [Name: glutathione-disulfide reductase activity]; GO:0004791 [Name: thioredoxin-disulfide reductase activity]; GO:0005829 [Name: cytosol]; GO:0050660 [Name: flavin adenine dinucleotide binding]; GO:0005739 [Name: mitochondrion]; GO:0034599 [Name: cellular response to oxidative stress]; GO:0006749 [Name: glutathione metabolic process]; GO:0045454 [Name: cell redox homeostasis]</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>thioredoxin reductase 1, cytoplasmic-like</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>LOC107443032</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>thioredoxin reductase 1, cytoplasmic isoform X1</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>LOC129221501</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>thioredoxin reductase 1, cytoplasmic-like</t>
         </is>
@@ -802,42 +930,90 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
+        <v>54925.8399197961</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.009999999999999998</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.249483997671434e-06</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2688797491349263</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.2539173898214765</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.5914792798336549</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1296409710314187</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.000278759523855833</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.02087873493297004</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.2276027607543095</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.2743807024586471</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.7721184797218347</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2.378997468343527</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>3.174590053279736</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AR3" t="n">
         <v>0.2351887188179091</v>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>129229604</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>GO:0032281 [Name: AMPA glutamate receptor complex]; GO:0005615 [Name: extracellular space]; GO:0030514 [Name: negative regulation of BMP signaling pathway]; GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>enolase-phosphatase E1-like</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>LOC107436697</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>uncharacterized protein isoform X4</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>LOC129229604</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>enolase-phosphatase E1-like isoform X1</t>
         </is>
@@ -927,42 +1103,90 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
+        <v>840232.2902577973</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.002269014604640992</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.571918063231641</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.3431019426020182</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.05597566579710356</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.6361535192920366</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.01847552350130435</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>210.2142446798641</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.08916235509577571</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.2226544092804725</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.9108376449042243</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2.808570095310327</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>0.2723600618782277</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AR4" t="n">
         <v>0.206148979937276</v>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>129222940</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>GO:0007165 [Name: signal transduction]</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>rho GTPase-activating protein 24-like</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>LOC107438170</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>uncharacterized protein</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>LOC129222940</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>rho GTPase-activating protein 24-like</t>
         </is>
@@ -1052,42 +1276,90 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
+        <v>3180.015432905307</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.004782485930508261</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.2031758061844969</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.7053439271248919</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.01706938167466288</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.2439180425815738</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.04595554436302606</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>105204.5021526676</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.0002745570295080661</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.08724098444396486</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.6890816009777878</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.4465744664380019</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.3106438419927041</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2.267209004846602</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>0.2223865884099506</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AR5" t="n">
         <v>0.2021702280205613</v>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>129228337</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>uncharacterized LOC129228337</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>LOC107442330</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>myosin-11 isoform X2</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>LOC129228337</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>uncharacterized protein LOC129228337</t>
         </is>
@@ -1177,42 +1449,90 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.0002023796697653495</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.1158783706695904</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.006766082672835243</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.8794700527634043</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.004449196897239979</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.0009255775055188317</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.007673373011749618</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.9719714329988006</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.01113051351004741</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.02710298949568057</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.394172123518836</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>0.01586027435583266</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AR6" t="n">
         <v>0.007809178301782454</v>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>129221589</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>GO:0004672 [Name: protein kinase activity]; GO:0005524 [Name: ATP binding]; GO:0006468 [Name: protein phosphorylation]</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>Serine/threonine-protein kinase Tao</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>LOC107448445</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>serine/threonine-protein kinase Tao</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>LOC129221589</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>serine/threonine-protein kinase Tao-like isoform X1</t>
         </is>
@@ -1302,42 +1622,90 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.0002174182739740385</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.04670493346214622</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.7017877898558712</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2907960799382956</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.2886070230499834</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.00938776882017142</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>21301.17075965319</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.008017820265224261</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2621467753521215</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.2049764110285767</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.7298354043826543</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.315719488299701</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>0.159752861054656</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AR7" t="n">
         <v>0.1528358491410604</v>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>129221272</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>GO:0005654 [Name: nucleoplasm]; GO:0042826 [Name: histone deacetylase binding]; GO:0000122 [Name: negative regulation of transcription from RNA polymerase II promoter]; GO:0003714 [Name: transcription corepressor activity]</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>mesoderm induction early response protein 2-like</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>LOC107453844</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>mesoderm induction early response protein 1 isoform X7</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>LOC129221272</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>mesoderm induction early response protein 2-like</t>
         </is>
@@ -1427,42 +1795,90 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
+        <v>4159.706470378802</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.009999999999999997</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.03510329611522273</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.2423185382515747</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.138306376870186</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.5669909070861953</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.18069055466223</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>737.9675762027106</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2912525450698032</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.3292011393873436</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.7087474549301968</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.792471425225224</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>0.4288452144836523</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AR8" t="n">
         <v>0.2386762125878368</v>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>129227321</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>GO:0030877 [Name: beta-catenin destruction complex]; GO:0045295 [Name: gamma-catenin binding]; GO:0090090 [Name: negative regulation of canonical Wnt signaling pathway]; GO:0045595 [Name: regulation of cell differentiation]; GO:0001708 [Name: cell fate specification]; GO:0005881 [Name: cytoplasmic microtubule]; GO:0016477 [Name: cell migration]; GO:0007399 [Name: nervous system development]; GO:0016342 [Name: catenin complex]; GO:0045732 [Name: positive regulation of protein catabolic process]; GO:0007026 [Name: negative regulation of microtubule depolymerization]; GO:0007389 [Name: pattern specification process]; GO:0008013 [Name: beta-catenin binding]; GO:0008017 [Name: microtubule binding]</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>adenomatous polyposis coli protein-like</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>LOC107446061</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>putative leucine-rich repeat-containing protein DDB_G0290503 isoform X3</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>LOC129227321</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>adenomatous polyposis coli protein-like</t>
         </is>
@@ -1552,42 +1968,90 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
+        <v>21982104.28500739</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.001296082491679138</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.1104925528301709</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9987039175083209</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.1096800927185775</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>300.0614463657143</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.0007768216935310556</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.09248881155090929</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.4215706081708026</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.1021631148025509</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.5776525701356663</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>3.569060116499334</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>0.2233932601719419</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AR9" t="n">
         <v>0.09801458412388261</v>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>129231876</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>GO:0061617 [Name: MICOS complex]; GO:0042407 [Name: cristae formation]</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>MICOS complex subunit MIC60-like</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>LOC107453361</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>MICOS complex subunit Mic60 isoform X1</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>LOC129231876</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>MICOS complex subunit MIC60-like isoform X1</t>
         </is>
@@ -1677,42 +2141,90 @@
         <v>0.06357473395786854</v>
       </c>
       <c r="AA10" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.005347821241550901</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.06078387442967458</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.6084430782932716</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.3361237812023825</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.05008531926279507</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>143.1886682128803</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.8550212479231593</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.4173943247181276</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.08132503353476622</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.5279139501652782</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.05469172511659429</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>0.6298215643591745</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AR10" t="n">
         <v>0.4839827811659705</v>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>129217694</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AT10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AU10" t="inlineStr">
         <is>
           <t>uncharacterized LOC129217694</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>LOC107439916</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>uncharacterized protein</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>LOC129217694</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>uncharacterized protein LOC129217694</t>
         </is>
@@ -1802,42 +2314,90 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
+        <v>184.9379020103529</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.009999999999999998</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.03619804491368202</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.4822159683039809</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.3940451277786974</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.4752799844760014</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.03250404722001773</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>30651.49019388387</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.0008416238900819993</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.1451757487339212</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.999158376109918</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.1437271124095409</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2.722344607097975</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>2.483741559365556</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AR11" t="n">
         <v>0.1510282482404832</v>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>129225869</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
         <is>
           <t>uncharacterized LOC129225869</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>LOC107453016</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>uncharacterized protein</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>LOC129225869</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>uncharacterized protein LOC129225869 isoform X2</t>
         </is>
@@ -1927,42 +2487,90 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
+        <v>100.0000000000152</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.2347641261438649</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.1059903598737683</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.8188130213048231</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.1811869786951769</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>189.2783768631443</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.3688856441028059</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.5184486005457556</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.03454318050801718</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.4815513994542444</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.279326429157755</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>0.306446626490573</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AR12" t="n">
         <v>0.2165513738026107</v>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>129224384</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AT12" t="inlineStr">
         <is>
           <t>GO:0005737 [Name: cytoplasm]; GO:0005515 [Name: protein binding]</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AU12" t="inlineStr">
         <is>
           <t>ankyrin repeat domain-containing protein 16-like</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>LOC110282259</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>uncharacterized protein</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>LOC129224385</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>uncharacterized protein LOC129224385</t>
         </is>
@@ -2052,42 +2660,90 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
+        <v>1449938.994272803</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.005224729486022807</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.1826362597635802</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.498788848244476</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.1632570334488395</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.3079322827232708</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.1880541395462303</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>437.1517330268414</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.0009171439212592978</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.00745653229953748</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.23081510007562</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.5254090754161063</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.7682677560031207</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>8.110020545077649</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>0.3904994375632912</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AR13" t="n">
         <v>0.4164911202066369</v>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AS13" t="inlineStr">
         <is>
           <t>129231445</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AT13" t="inlineStr">
         <is>
           <t>GO:0032807 [Name: DNA ligase IV complex]; GO:0006303 [Name: double-strand break repair via nonhomologous end joining]; GO:0045027 [Name: DNA end binding]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AU13" t="inlineStr">
         <is>
           <t>uncharacterized LOC129231445</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AV13" t="inlineStr">
         <is>
           <t>LOC107440379</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>uncharacterized protein</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>LOC129231445</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>uncharacterized protein LOC129231445</t>
         </is>
@@ -2177,42 +2833,90 @@
         <v>0.1570859179283945</v>
       </c>
       <c r="AA14" t="n">
+        <v>1115901.181739209</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.009999999999999995</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.2531868444054347</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.2680524325974601</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.5456665012828454</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.1911466543117198</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>136.8721221652831</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.5963590429762836</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.517758820388097</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.400619366402979</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.0816218132089241</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>0.4306258001254727</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AR14" t="n">
         <v>0.4040678876536797</v>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AS14" t="inlineStr">
         <is>
           <t>129234407</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AT14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AU14" t="inlineStr">
         <is>
           <t>uncharacterized LOC129234407</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AV14" t="inlineStr">
         <is>
           <t>LOC107446559</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AW14" t="inlineStr">
         <is>
           <t>uncharacterized protein isoform X3</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>LOC129234407</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>uncharacterized protein LOC129234407 isoform X1</t>
         </is>
@@ -2302,42 +3006,90 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
+        <v>10973.640194968</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.002227248636032506</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.2599516826659437</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.2394861349179187</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.05030073847181565</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.5405508452455725</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.2177357712004762</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>270739.3730015687</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.001132461821735576</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.3006962172526915</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.29203103930138</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.698171320925573</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>2.265249149032002</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>0.3575042053518293</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AR15" t="n">
         <v>0.2086760706089999</v>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AS15" t="inlineStr">
         <is>
           <t>129223223</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AT15" t="inlineStr">
         <is>
           <t>GO:0034097 [Name: response to cytokine]; GO:0003700 [Name: transcription factor activity, sequence-specific DNA binding]; GO:0006355 [Name: regulation of transcription, DNA-templated]; GO:0033554 [Name: cellular response to stress]; GO:0003677 [Name: DNA binding]; GO:0007249 [Name: I-kappaB kinase/NF-kappaB signaling]; GO:0038061 [Name: NIK/NF-kappaB signaling]; GO:0006954 [Name: inflammatory response]; GO:0005515 [Name: protein binding]; GO:0005737 [Name: cytoplasm]; GO:0045087 [Name: innate immune response]</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AU15" t="inlineStr">
         <is>
           <t>nuclear factor NF-kappa-B p105 subunit-like</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AV15" t="inlineStr">
         <is>
           <t>LOC107451409</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AW15" t="inlineStr">
         <is>
           <t>nuclear factor NF-kappa-B p100 subunit</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>LOC129223223</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>nuclear factor NF-kappa-B p105 subunit-like</t>
         </is>
@@ -2427,42 +3179,90 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
+        <v>1017.569925610293</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.009999999999999998</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.4014197365216434</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.02963423083402224</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.5700163378802127</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.01856392559814387</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>139.9952737549192</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.4580668452967772</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.6529541497226961</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.3470458502773039</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2.280348599777973</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>1.900651000794934</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AR16" t="n">
         <v>0.3125375559389879</v>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AS16" t="inlineStr">
         <is>
           <t>129219249</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AT16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AU16" t="inlineStr">
         <is>
           <t>homeobox protein 2-like</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AV16" t="inlineStr">
         <is>
           <t>LOC107453506</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AW16" t="inlineStr">
         <is>
           <t>probable serine/threonine-protein kinase clkA isoform X1</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>LOC129219249</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>homeobox protein 2-like</t>
         </is>
@@ -2552,42 +3352,90 @@
         <v>0.01842974293947454</v>
       </c>
       <c r="AA17" t="n">
+        <v>14521.14389928709</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.00310629023373191</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.1252836573897144</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.3560434987389038</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.1261993313347753</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.5610579071943277</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.07979230383303673</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.0005111384514442333</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.04513452228509037</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.6300537198789412</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.2281522526962544</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.3535916319722827</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>3.27565048374091</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.01584350969733192</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>0.2352539893954525</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AR17" t="n">
         <v>0.1649400649377632</v>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AS17" t="inlineStr">
         <is>
           <t>129230333</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AT17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AU17" t="inlineStr">
         <is>
           <t>titin-like</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AV17" t="inlineStr">
         <is>
           <t>LOC107454808</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AW17" t="inlineStr">
         <is>
           <t>titin-like</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>LOC129230333</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>titin-like</t>
         </is>
@@ -2677,42 +3525,90 @@
         <v>0.004518900562626565</v>
       </c>
       <c r="AA18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.00574641461079801</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.1035344687206496</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.6604713219531569</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.1282276178804068</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.2725565302035025</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.06122573323254245</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>373.0693370240828</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.04063312359714528</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.6112408702750989</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.1992429900433554</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.3887591297249011</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.010474576333039</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>0.4209855744071893</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AR18" t="n">
         <v>0.104636023779777</v>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AS18" t="inlineStr">
         <is>
           <t>129223000</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AT18" t="inlineStr">
         <is>
           <t>GO:0005615 [Name: extracellular space]</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AU18" t="inlineStr">
         <is>
           <t>uncharacterized LOC129223000</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AV18" t="inlineStr">
         <is>
           <t>LOC107442673</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AW18" t="inlineStr">
         <is>
           <t>uncharacterized protein</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>LOC129223000</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>uncharacterized protein LOC129223000</t>
         </is>
@@ -2802,42 +3698,90 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.0002470704975962378</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.06383203316518056</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9695603852604869</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.0933145337496489</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.005648855532258048</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.02454368870965884</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.000231217911725031</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.06401895916659496</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.999768782088275</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.1841897851812869</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>2.28128119722613</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>0.1001861409580952</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AR19" t="n">
         <v>0.06421245890787448</v>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AS19" t="inlineStr">
         <is>
           <t>129235321</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AT19" t="inlineStr">
         <is>
           <t>GO:0003730 [Name: mRNA 3'-UTR binding]; GO:0005634 [Name: nucleus]; GO:0008135 [Name: translation factor activity, RNA binding]; GO:0045202 [Name: synapse]; GO:2000766 [Name: negative regulation of cytoplasmic translation]; GO:0043005 [Name: neuron projection]; GO:0000900 [Name: translation repressor activity, nucleic acid binding]; GO:0043022 [Name: ribosome binding]; GO:0005737 [Name: cytoplasm]</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AU19" t="inlineStr">
         <is>
           <t>polyadenylation element binding protein orb</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AV19" t="inlineStr">
         <is>
           <t>LOC107437559</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>cytoplasmic polyadenylation element-binding protein 1 isoform X1</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>LOC129235321</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>cytoplasmic polyadenylation element-binding protein 1-like isoform X1</t>
         </is>
@@ -2927,30 +3871,78 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
+        <v>223670.6755270619</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.0004045710065605148</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.223076313346779e-05</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.995396006379757</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.004199422613682449</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1756.303614012077</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.0007965981126223469</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.3288636566760231</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.001692919810199983</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.671136343323977</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>4.726758100891828</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>0.01451644658203786</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AR20" t="n">
         <v>0.001396164449013093</v>
       </c>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr">
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr">
         <is>
           <t>LOC107453013</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AW20" t="inlineStr">
         <is>
           <t>AP-2 complex subunit sigma</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>LOC129221226</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>AP-1 complex subunit sigma-2-like</t>
         </is>
@@ -3040,30 +4032,78 @@
         <v>0.03231810139125735</v>
       </c>
       <c r="AA21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.003818831410806006</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.2931028210263213</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.2195994627505375</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.5074472829348045</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.1956310646280684</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>212.768294887159</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.5377846450355837</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.3322645754278657</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.1343419327187082</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.6578610022257816</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.009874422346352716</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>0.4012934504368504</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AR21" t="n">
         <v>0.2847337623988047</v>
       </c>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr">
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr">
         <is>
           <t>NO_HIT</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AW21" t="inlineStr">
         <is>
           <t>NO_HIT</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>NO_HIT</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>NO_HIT</t>
         </is>
@@ -3153,30 +4193,78 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
+        <v>440.8983780503327</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.1246279434468194</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.2506478018340251</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.1673342817400029</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.5903772929637916</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.1589749052021833</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>144.994688078085</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.058791184067875e-22</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.1952920544590448</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.973521846816108</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.20177394981126</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.02647815318389202</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>6.82657919261942</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>0.4388495853124726</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AR22" t="n">
         <v>0.2026760338450765</v>
       </c>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr">
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr">
         <is>
           <t>NO_HIT</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AW22" t="inlineStr">
         <is>
           <t>NO_HIT</t>
         </is>
       </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>LOC129223840</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AY22" t="inlineStr">
         <is>
           <t>RNA-binding protein 4.1-like isoform X1</t>
         </is>
@@ -3266,30 +4354,78 @@
         <v>0.1922443612732636</v>
       </c>
       <c r="AA23" t="n">
+        <v>8823.573130703106</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.0007809913636614323</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.02912411746118326</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.3316442861228987</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.1923332781314468</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.465140389013352</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.2024343335000878</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>74351.93723271979</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.0004733249523741046</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.0002737359844730716</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.4545725003244224</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.4164848117131321</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.4008933175157625</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.1440608572074411</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>0.330418767577735</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AR23" t="n">
         <v>0.3207959684002702</v>
       </c>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr">
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr">
         <is>
           <t>LOC107451375</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AW23" t="inlineStr">
         <is>
           <t>PWWP domain-containing DNA repair factor 3A</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>NO_HIT</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>NO_HIT</t>
         </is>
@@ -3379,30 +4515,78 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
+        <v>1288.460260184059</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.009999999999999998</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.004397638511552522</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.3002902643768202</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.1854238072778232</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.253437632331207</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.4362721032919727</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>265458055.7690743</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.0006628240790764054</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.166328718204955</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.4585562747153693</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.8330084577159687</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>2.288073357551616</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>0.6417909413357693</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AR24" t="n">
         <v>0.3966528166932235</v>
       </c>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr">
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr">
         <is>
           <t>LOC107455578</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AW24" t="inlineStr">
         <is>
           <t>uro-adherence factor A</t>
         </is>
       </c>
-      <c r="AH24" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>NO_HIT</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>NO_HIT</t>
         </is>
